--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62358.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62358.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>1G.1103</t>
+          <t>KG.1103</t>
         </is>
       </c>
     </row>
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>07/08/2028</t>
         </is>
       </c>
     </row>
@@ -465,7 +465,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S1-01-G1</t>
+          <t>S1-01-01</t>
         </is>
       </c>
     </row>
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Uuuuluuluv</t>
+          <t>Tnjian</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ILULV</t>
+          <t>LPI</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G00D</t>
+          <t>G00B</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52347</v>
+        <v>62358</v>
       </c>
     </row>
     <row r="18">

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62358.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62358.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/08/2028</t>
+          <t>17/11/2025</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="10">
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G00B</t>
+          <t>G00A</t>
         </is>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62358.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62358.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tnjian</t>
+          <t>Trstan</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LPI</t>
+          <t>PAI</t>
         </is>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62358.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62358.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Trstan</t>
+          <t>TRSTAN</t>
         </is>
       </c>
     </row>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62358.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62358.xlsx
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1110</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
